--- a/Modules/LOGx/LOGx_BOM.xlsx
+++ b/Modules/LOGx/LOGx_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Dev\Modular Synth\Avalon Harmonics\LOGx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CA3190-161A-4AC2-8EC5-97123814C419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E226037E-8124-4910-A2E5-947675DCB0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -184,15 +184,9 @@
     <t>Pushernut</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/black-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/pushernuts-gold-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>4081 - AND</t>
   </si>
   <si>
@@ -354,9 +348,6 @@
     <t>https://www.tme.eu/de/en/details/zl201-40g/pin-headers/connfly/ds1021-1-40sf11-b/</t>
   </si>
   <si>
-    <t>https://www.tme.eu/de/en/details/zl202-80g/pin-headers/connfly/ds1021-2-40sf11/</t>
-  </si>
-  <si>
     <t>https://www.tme.eu/de/en/details/icvt-8p/standard-dip-sockets/connfly/ds1009-08at1nx/</t>
   </si>
   <si>
@@ -807,6 +798,15 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>https://www.tme.eu/de/en/details/zl202-10g/pin-headers/connfly/ds1021-2-5sf11-b/</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57164621578504</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57166910816520</t>
   </si>
 </sst>
 </file>
@@ -1719,7 +1719,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1754,16 +1754,16 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s">
         <v>29</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>47</v>
@@ -1777,16 +1777,16 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E4" t="s">
         <v>29</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>47</v>
@@ -1800,7 +1800,7 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
         <v>20</v>
@@ -1809,7 +1809,7 @@
         <v>29</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>47</v>
@@ -1823,16 +1823,16 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
         <v>29</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>47</v>
@@ -1846,19 +1846,19 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
         <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1869,19 +1869,19 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
         <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J8" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -1901,10 +1901,10 @@
         <v>30</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1918,16 +1918,16 @@
         <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
         <v>31</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1947,7 +1947,7 @@
         <v>44</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>48</v>
@@ -1970,7 +1970,7 @@
         <v>44</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>48</v>
@@ -1993,10 +1993,10 @@
         <v>25</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -2016,10 +2016,10 @@
         <v>24</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J14" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -2027,13 +2027,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
         <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
@@ -2042,7 +2042,7 @@
         <v>49</v>
       </c>
       <c r="J15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -2062,10 +2062,10 @@
         <v>34</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J16" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -2079,16 +2079,16 @@
         <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E17" t="s">
         <v>16</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J17" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -2096,13 +2096,13 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
         <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E18" t="s">
         <v>33</v>
@@ -2111,7 +2111,7 @@
         <v>51</v>
       </c>
       <c r="J18" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2119,10 +2119,10 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
         <v>38</v>
@@ -2131,10 +2131,10 @@
         <v>32</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J19" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2142,22 +2142,22 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E20" t="s">
         <v>32</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -2165,10 +2165,10 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
         <v>19</v>
@@ -2177,10 +2177,10 @@
         <v>32</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="J21" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2188,19 +2188,19 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" t="s">
         <v>68</v>
       </c>
-      <c r="C23" t="s">
+      <c r="F23" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E23" t="s">
-        <v>70</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>71</v>
-      </c>
       <c r="J23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2208,19 +2208,19 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" t="s">
         <v>72</v>
       </c>
-      <c r="C24" t="s">
+      <c r="F24" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E24" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="J24" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2228,19 +2228,19 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" t="s">
         <v>76</v>
       </c>
-      <c r="C25" t="s">
+      <c r="F25" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E25" t="s">
-        <v>78</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="J25" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2254,13 +2254,13 @@
         <v>53</v>
       </c>
       <c r="E27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="J27" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2268,19 +2268,19 @@
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C28" t="s">
         <v>53</v>
       </c>
       <c r="E28" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="J28" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2288,7 +2288,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -2296,42 +2296,42 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B32" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2355,18 +2355,18 @@
     <hyperlink ref="F23" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
     <hyperlink ref="F24" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
     <hyperlink ref="F25" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="F27" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="F28" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="J20" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="F19" r:id="rId23" xr:uid="{E3E9128E-171B-4FF8-B2F8-635CA7A74ECB}"/>
-    <hyperlink ref="F21" r:id="rId24" xr:uid="{94C7BCC7-8F2B-4815-B1C7-0D2EB204A468}"/>
-    <hyperlink ref="F3" r:id="rId25" xr:uid="{CA81EE03-392C-4D6D-83EA-F768127A766D}"/>
-    <hyperlink ref="F4" r:id="rId26" xr:uid="{7CCE59AB-5574-4899-AF1C-60294F37EAB3}"/>
-    <hyperlink ref="F5" r:id="rId27" xr:uid="{6FD7CC5D-6E47-4085-886C-419741D1BAC9}"/>
-    <hyperlink ref="F6" r:id="rId28" xr:uid="{A24C1976-4BF8-4BA1-A4CD-81BFC7716665}"/>
-    <hyperlink ref="F12" r:id="rId29" xr:uid="{00C710CC-AF6F-4729-AA11-4AF64F5A9AB4}"/>
-    <hyperlink ref="F11" r:id="rId30" xr:uid="{6D16DF2D-3579-406D-90CF-3EE18407FB17}"/>
-    <hyperlink ref="F20" r:id="rId31" xr:uid="{39E95F6B-57E8-4CBC-94A5-26433D6BC7FD}"/>
+    <hyperlink ref="J20" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="F19" r:id="rId21" xr:uid="{E3E9128E-171B-4FF8-B2F8-635CA7A74ECB}"/>
+    <hyperlink ref="F3" r:id="rId22" xr:uid="{CA81EE03-392C-4D6D-83EA-F768127A766D}"/>
+    <hyperlink ref="F4" r:id="rId23" xr:uid="{7CCE59AB-5574-4899-AF1C-60294F37EAB3}"/>
+    <hyperlink ref="F5" r:id="rId24" xr:uid="{6FD7CC5D-6E47-4085-886C-419741D1BAC9}"/>
+    <hyperlink ref="F6" r:id="rId25" xr:uid="{A24C1976-4BF8-4BA1-A4CD-81BFC7716665}"/>
+    <hyperlink ref="F12" r:id="rId26" xr:uid="{00C710CC-AF6F-4729-AA11-4AF64F5A9AB4}"/>
+    <hyperlink ref="F11" r:id="rId27" xr:uid="{6D16DF2D-3579-406D-90CF-3EE18407FB17}"/>
+    <hyperlink ref="F20" r:id="rId28" xr:uid="{39E95F6B-57E8-4CBC-94A5-26433D6BC7FD}"/>
+    <hyperlink ref="F21" r:id="rId29" xr:uid="{FAB8D7D9-9B79-475E-90ED-C0716E2AAFCD}"/>
+    <hyperlink ref="F27" r:id="rId30" xr:uid="{4F681CB4-D07E-4AF5-94C6-70FC93339770}"/>
+    <hyperlink ref="F28" r:id="rId31" xr:uid="{B7F498A7-F98C-46AC-8CDD-E36ACB06789F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
